--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-03-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-03-2026.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>£11.28</t>
+          <t>£12.97</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>£13.05</t>
+          <t>£15.01</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>£16.05</t>
+          <t>£18.46</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>£17.83</t>
+          <t>£20.50</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>£21.36</t>
+          <t>£24.56</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>£23.13</t>
+          <t>£30.44</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>£23.53</t>
+          <t>£27.06</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>£25.89</t>
+          <t>£29.77</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>£33.90</t>
+          <t>£38.99</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>£29.72</t>
+          <t>£34.18</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>£56.06</t>
+          <t>£64.47</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>£35.79</t>
+          <t>£41.16</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>£40.85</t>
+          <t>£46.98</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>£44.28</t>
+          <t>£50.92</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>£43.42</t>
+          <t>£49.93</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>£1055.68</t>
+          <t>£1214.04</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>£1280.46</t>
+          <t>£1472.52</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
